--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A85AD62-33F6-406A-808C-35A00CAB1359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9194D638-268D-479A-9E85-F8C3FF48EABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>LP</t>
   </si>
@@ -28,28 +28,139 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-048900</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-046959</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
-  </si>
-  <si>
-    <t>LP-047189</t>
-  </si>
-  <si>
-    <t>LP-049042</t>
-  </si>
-  <si>
-    <t>LP-049048</t>
-  </si>
-  <si>
-    <t>LP-049115</t>
+    <t>LP-039073</t>
+  </si>
+  <si>
+    <t>LP-046105</t>
+  </si>
+  <si>
+    <t>LP-046956</t>
+  </si>
+  <si>
+    <t>LP-047519</t>
+  </si>
+  <si>
+    <t>LP-047644</t>
+  </si>
+  <si>
+    <t>LP-047828</t>
+  </si>
+  <si>
+    <t>LP-048165</t>
+  </si>
+  <si>
+    <t>LP-048166</t>
+  </si>
+  <si>
+    <t>LP-048649</t>
+  </si>
+  <si>
+    <t>LP-048978</t>
+  </si>
+  <si>
+    <t>LP-049197</t>
+  </si>
+  <si>
+    <t>LP-049211</t>
+  </si>
+  <si>
+    <t>LP-049348</t>
+  </si>
+  <si>
+    <t>LP-049450</t>
+  </si>
+  <si>
+    <t>LP-049453</t>
+  </si>
+  <si>
+    <t>LP-049455</t>
+  </si>
+  <si>
+    <t>LP-049500</t>
+  </si>
+  <si>
+    <t>LP-049674</t>
+  </si>
+  <si>
+    <t>LP-047288</t>
+  </si>
+  <si>
+    <t>LP-047289</t>
+  </si>
+  <si>
+    <t>LP-047922</t>
+  </si>
+  <si>
+    <t>LP-048949</t>
+  </si>
+  <si>
+    <t>LP-049086</t>
+  </si>
+  <si>
+    <t>LP-049241</t>
+  </si>
+  <si>
+    <t>LP-049439</t>
+  </si>
+  <si>
+    <t>LP-048498</t>
+  </si>
+  <si>
+    <t>LP-049711</t>
+  </si>
+  <si>
+    <t>LP-049794</t>
+  </si>
+  <si>
+    <t>LP-049866</t>
+  </si>
+  <si>
+    <t>LP-049900</t>
+  </si>
+  <si>
+    <t>LP-049906</t>
+  </si>
+  <si>
+    <t>LP-049944</t>
+  </si>
+  <si>
+    <t>LP-049978</t>
+  </si>
+  <si>
+    <t>LP-049980</t>
+  </si>
+  <si>
+    <t>LP-050051</t>
+  </si>
+  <si>
+    <t>LP-050067</t>
+  </si>
+  <si>
+    <t>LP-050072</t>
+  </si>
+  <si>
+    <t>LP-050118</t>
+  </si>
+  <si>
+    <t>LP-050102</t>
+  </si>
+  <si>
+    <t>LP-050168</t>
+  </si>
+  <si>
+    <t>LP-050266</t>
+  </si>
+  <si>
+    <t>LP-050286</t>
+  </si>
+  <si>
+    <t>LP-050489</t>
+  </si>
+  <si>
+    <t>LP-050542</t>
+  </si>
+  <si>
+    <t>LP-050577</t>
   </si>
 </sst>
 </file>
@@ -412,11 +523,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -431,48 +542,225 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="s">
-        <v>3</v>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,606 +443,554 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP-042605</t>
+          <t>LP-049701</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Encerrado!</t>
+          <t>Compromisso pendente!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP-045880</t>
+          <t>LP-049802</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Encerrado!</t>
+          <t>Compromisso pendente!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP-046158</t>
+          <t>LP-049808</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Encerrado!</t>
+          <t>Compromisso pendente!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP-048214</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>LP-049869</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Compromisso pendente!</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP-048388</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>LP-049986</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP-048523</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>LP-050022</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP-048524</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>LP-050074</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP-048853</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>LP-050101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP-048852</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>LP-050107</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP-048995</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>LP-050221</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP-049083</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>LP-050265</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP-049171</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>LP-050288</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP-049174</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>LP-050289</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP-049176</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>LP-050291</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP-049233</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>LP-050295</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP-049294</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>LP-050306</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP-049537</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>LP-050307</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LP-049557</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>LP-050329</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LP-049592</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>LP-050330</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LP-049701</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>LP-050340</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LP-049713</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>LP-050345</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LP-049719</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>LP-050346</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LP-049802</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>LP-050362</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LP-049808</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>LP-050481</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LP-049869</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>LP-050492</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LP-049920</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>LP-050558</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Compromisso pendente!</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LP-049925</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>LP-050559</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Compromisso pendente!</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LP-049926</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>LP-050575</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LP-049927</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>LP-050843</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Compromisso pendente!</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LP-049949</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>LP-043689</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LP-049951</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>LP-045882</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LP-049981</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>LP-047197</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LP-049986</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>LP-048173</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LP-050022</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>LP-048269</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LP-050074</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>LP-048512</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LP-050101</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>LP-049045</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LP-050107</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>LP-049296</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LP-050221</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>LP-049317</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LP-050265</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>LP-049374</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LP-050288</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>LP-049390</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LP-050289</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>LP-049503</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LP-050291</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>LP-049649</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LP-050295</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>LP-049665</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LP-050306</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>LP-049756</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LP-050307</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>LP-049863</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LP-050329</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>LP-050330</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>LP-050340</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>LP-050345</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LP-050346</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LP-050362</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>LP-050481</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>LP-050492</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>LP-050558</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>LP-050559</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>LP-050575</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>LP-050843</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>LP-043689</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>LP-045882</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>LP-047197</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>LP-048173</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>LP-048269</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>LP-048512</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>LP-049045</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>LP-049296</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>LP-049317</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>LP-049374</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>LP-049390</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>LP-049503</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>LP-049649</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>LP-049665</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>LP-049756</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>LP-049863</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
           <t>LP-050157</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Encerrado!</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B114"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,31 +443,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LP-049686</t>
+          <t>LP-047469</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LP-049692</t>
+          <t>LP-047772</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LP-049767</t>
+          <t>LP-047831</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LP-049847</t>
+          <t>LP-048378</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LP-049862</t>
+          <t>LP-048658</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -503,19 +503,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LP-049935</t>
+          <t>LP-048735</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LP-045624</t>
+          <t>LP-048736</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -527,31 +527,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LP-050034</t>
+          <t>LP-048976</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LP-050035</t>
+          <t>LP-048981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LP-050128</t>
+          <t>LP-049324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LP-050133</t>
+          <t>LP-049349</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LP-050142</t>
+          <t>LP-049370</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LP-050175</t>
+          <t>LP-049384</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -599,19 +599,19 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LP-050229</t>
+          <t>LP-049835</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LP-050230</t>
+          <t>LP-049837</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -623,19 +623,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LP-050235</t>
+          <t>LP-049844</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LP-050255</t>
+          <t>LP-049845</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -647,19 +647,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LP-050275</t>
+          <t>LP-049846</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LP-050378</t>
+          <t>LP-049859</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LP-050384</t>
+          <t>LP-049993</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LP-050385</t>
+          <t>LP-050032</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LP-050386</t>
+          <t>LP-050033</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LP-050387</t>
+          <t>LP-050136</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LP-044259</t>
+          <t>LP-050140</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LP-047084</t>
+          <t>LP-050236</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -743,7 +743,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LP-047280</t>
+          <t>LP-050299</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -755,31 +755,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LP-047413</t>
+          <t>LP-050379</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Compromisso pendente!</t>
+          <t>Encerrado!</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LP-047414</t>
+          <t>LP-041331</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Encerrado!</t>
+          <t>Compromisso pendente!</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LP-047966</t>
+          <t>LP-045379</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LP-047967</t>
+          <t>LP-045689</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LP-047969</t>
+          <t>LP-046208</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LP-047973</t>
+          <t>LP-046856</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -827,7 +827,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LP-047974</t>
+          <t>LP-046871</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -839,31 +839,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LP-048027</t>
+          <t>LP-047546</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Encerrado!</t>
+          <t>Compromisso pendente!</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LP-048041</t>
+          <t>LP-047961</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Encerrado!</t>
+          <t>Compromisso pendente!</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LP-048076</t>
+          <t>LP-047994</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -875,926 +875,706 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LP-048239</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048234</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LP-048319</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048235</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LP-048461</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048237</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LP-048525</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048358</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LP-048546</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048446</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LP-048576</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048460</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LP-048588</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-048469</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LP-048591</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048475</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LP-048593</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048483</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LP-048594</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048667</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LP-048595</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048669</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LP-048596</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048689</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LP-048645</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048876</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LP-048655</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048900</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LP-048657</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-048977</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LP-048712</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049054</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LP-048859</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049089</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LP-048902</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049144</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LP-049062</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049279</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LP-049063</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049405</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LP-049064</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049408</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LP-049065</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049681</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LP-049066</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049697</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LP-049068</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-049698</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LP-049069</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049718</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LP-049070</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049721</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LP-049072</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049722</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LP-049079</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049797</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LP-049082</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049803</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LP-049084</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049804</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LP-049087</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049865</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>LP-049088</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049820</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LP-049090</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049867</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LP-049113</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049876</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>LP-049245</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-049878</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LP-049301</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049879</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LP-049302</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049905</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LP-049303</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049924</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LP-049409</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-049941</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LP-049496</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050036</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>LP-049498</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050063</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LP-049775</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050111</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LP-049778</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050121</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LP-049817</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050122</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>LP-049886</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050149</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LP-049894</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050165</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LP-049916</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050214</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>LP-049988</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050215</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>LP-050063</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050218</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LP-050076</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050219</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LP-050677</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050220</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>LP-050078</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050223</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>LP-050079</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050225</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>LP-050080</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050240</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>LP-050081</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050287</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>LP-050178</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050293</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LP-050201</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050294</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LP-050250</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050326</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LP-050321</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050327</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LP-050495</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050335</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LP-050497</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050336</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LP-050499</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050352</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LP-050543</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050368</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LP-050588</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050473</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LP-050638</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050500</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LP-050641</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050507</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>LP-050703</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050530</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LP-050704</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050531</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LP-050807</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050534</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LP-050808</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050556</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LP-050809</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050557</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LP-050810</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050562</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LP-050811</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050580</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LP-050812</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050587</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LP-050846</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050596</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LP-050885</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Compromisso pendente!</t>
-        </is>
-      </c>
+          <t>LP-050618</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LP-050919</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Encerrado!</t>
-        </is>
-      </c>
+          <t>LP-050700</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>LP-050702</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>LP-050727</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>LP-050799</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>LP-050800</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>LP-050876</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>LP-050881</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>LP-051058</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>LP-051104</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>LP-051106</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>LP-051188</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>LP-051194</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{267E0D5B-CD6B-4E9F-8B3D-49A1A18DF6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9D6186-2A82-4E9E-B942-D03602A78557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$32</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>LP</t>
   </si>
@@ -49,202 +52,19 @@
     <t>LP-048235</t>
   </si>
   <si>
-    <t>LP-048237</t>
-  </si>
-  <si>
-    <t>LP-048358</t>
-  </si>
-  <si>
     <t>LP-048446</t>
   </si>
   <si>
     <t>LP-048460</t>
   </si>
   <si>
-    <t>LP-048469</t>
-  </si>
-  <si>
-    <t>LP-048475</t>
-  </si>
-  <si>
-    <t>LP-048483</t>
-  </si>
-  <si>
-    <t>LP-048667</t>
-  </si>
-  <si>
-    <t>LP-048669</t>
-  </si>
-  <si>
-    <t>LP-048689</t>
-  </si>
-  <si>
-    <t>LP-048876</t>
-  </si>
-  <si>
-    <t>LP-048900</t>
-  </si>
-  <si>
-    <t>LP-048977</t>
-  </si>
-  <si>
-    <t>LP-049054</t>
-  </si>
-  <si>
-    <t>LP-049089</t>
-  </si>
-  <si>
-    <t>LP-049144</t>
-  </si>
-  <si>
-    <t>LP-049279</t>
-  </si>
-  <si>
-    <t>LP-049405</t>
-  </si>
-  <si>
-    <t>LP-049408</t>
-  </si>
-  <si>
-    <t>LP-049681</t>
-  </si>
-  <si>
-    <t>LP-049697</t>
-  </si>
-  <si>
-    <t>LP-049698</t>
-  </si>
-  <si>
-    <t>LP-049718</t>
-  </si>
-  <si>
-    <t>LP-049721</t>
-  </si>
-  <si>
-    <t>LP-049722</t>
-  </si>
-  <si>
     <t>LP-049797</t>
   </si>
   <si>
-    <t>LP-049803</t>
-  </si>
-  <si>
-    <t>LP-049804</t>
-  </si>
-  <si>
-    <t>LP-049865</t>
-  </si>
-  <si>
-    <t>LP-049820</t>
-  </si>
-  <si>
-    <t>LP-049867</t>
-  </si>
-  <si>
-    <t>LP-049876</t>
-  </si>
-  <si>
-    <t>LP-049878</t>
-  </si>
-  <si>
-    <t>LP-049879</t>
-  </si>
-  <si>
-    <t>LP-049905</t>
-  </si>
-  <si>
-    <t>LP-049924</t>
-  </si>
-  <si>
-    <t>LP-049941</t>
-  </si>
-  <si>
-    <t>LP-050036</t>
-  </si>
-  <si>
-    <t>LP-050063</t>
-  </si>
-  <si>
-    <t>LP-050111</t>
-  </si>
-  <si>
-    <t>LP-050121</t>
-  </si>
-  <si>
-    <t>LP-050122</t>
-  </si>
-  <si>
-    <t>LP-050149</t>
-  </si>
-  <si>
-    <t>LP-050165</t>
-  </si>
-  <si>
-    <t>LP-050214</t>
-  </si>
-  <si>
-    <t>LP-050215</t>
-  </si>
-  <si>
-    <t>LP-050218</t>
-  </si>
-  <si>
-    <t>LP-050219</t>
-  </si>
-  <si>
-    <t>LP-050220</t>
-  </si>
-  <si>
-    <t>LP-050223</t>
-  </si>
-  <si>
-    <t>LP-050225</t>
-  </si>
-  <si>
-    <t>LP-050240</t>
-  </si>
-  <si>
-    <t>LP-050287</t>
-  </si>
-  <si>
-    <t>LP-050293</t>
-  </si>
-  <si>
-    <t>LP-050294</t>
-  </si>
-  <si>
-    <t>LP-050326</t>
-  </si>
-  <si>
-    <t>LP-050327</t>
-  </si>
-  <si>
-    <t>LP-050335</t>
-  </si>
-  <si>
-    <t>LP-050336</t>
-  </si>
-  <si>
-    <t>LP-050352</t>
-  </si>
-  <si>
-    <t>LP-050368</t>
-  </si>
-  <si>
-    <t>LP-050473</t>
-  </si>
-  <si>
     <t>LP-050500</t>
   </si>
   <si>
-    <t>LP-050507</t>
-  </si>
-  <si>
     <t>LP-050530</t>
-  </si>
-  <si>
-    <t>LP-050531</t>
   </si>
   <si>
     <t>LP-050534</t>
@@ -667,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -718,36 +538,57 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -847,311 +688,6 @@
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9D6186-2A82-4E9E-B942-D03602A78557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C44A486-9BC1-40AF-A907-83E1545C44B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$32</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>LP</t>
   </si>
@@ -67,39 +64,18 @@
     <t>LP-050530</t>
   </si>
   <si>
-    <t>LP-050534</t>
-  </si>
-  <si>
     <t>LP-050556</t>
   </si>
   <si>
-    <t>LP-050557</t>
-  </si>
-  <si>
-    <t>LP-050562</t>
-  </si>
-  <si>
     <t>LP-050580</t>
   </si>
   <si>
-    <t>LP-050587</t>
-  </si>
-  <si>
-    <t>LP-050596</t>
-  </si>
-  <si>
     <t>LP-050618</t>
   </si>
   <si>
     <t>LP-050700</t>
   </si>
   <si>
-    <t>LP-050702</t>
-  </si>
-  <si>
-    <t>LP-050727</t>
-  </si>
-  <si>
     <t>LP-050799</t>
   </si>
   <si>
@@ -107,9 +83,6 @@
   </si>
   <si>
     <t>LP-050876</t>
-  </si>
-  <si>
-    <t>LP-050881</t>
   </si>
   <si>
     <t>LP-051058</t>
@@ -487,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -594,100 +567,84 @@
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C44A486-9BC1-40AF-A907-83E1545C44B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C4203B-9EA7-4FAA-BAAD-9F90BC39DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>LP</t>
   </si>
@@ -86,18 +86,6 @@
   </si>
   <si>
     <t>LP-051058</t>
-  </si>
-  <si>
-    <t>LP-051104</t>
-  </si>
-  <si>
-    <t>LP-051106</t>
-  </si>
-  <si>
-    <t>LP-051188</t>
-  </si>
-  <si>
-    <t>LP-051194</t>
   </si>
 </sst>
 </file>
@@ -460,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -627,26 +615,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C4203B-9EA7-4FAA-BAAD-9F90BC39DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607DF85D-F68D-4E0F-872F-0EB660D497EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>LP</t>
   </si>
@@ -28,64 +28,346 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-041331</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-047546</t>
-  </si>
-  <si>
-    <t>LP-047961</t>
-  </si>
-  <si>
-    <t>LP-047994</t>
-  </si>
-  <si>
-    <t>LP-048234</t>
-  </si>
-  <si>
-    <t>LP-048235</t>
-  </si>
-  <si>
-    <t>LP-048446</t>
-  </si>
-  <si>
-    <t>LP-048460</t>
-  </si>
-  <si>
-    <t>LP-049797</t>
-  </si>
-  <si>
-    <t>LP-050500</t>
-  </si>
-  <si>
-    <t>LP-050530</t>
-  </si>
-  <si>
-    <t>LP-050556</t>
-  </si>
-  <si>
-    <t>LP-050580</t>
-  </si>
-  <si>
-    <t>LP-050618</t>
-  </si>
-  <si>
-    <t>LP-050700</t>
-  </si>
-  <si>
-    <t>LP-050799</t>
-  </si>
-  <si>
-    <t>LP-050800</t>
-  </si>
-  <si>
-    <t>LP-050876</t>
-  </si>
-  <si>
-    <t>LP-051058</t>
+    <t>LP-046242</t>
+  </si>
+  <si>
+    <t>LP-046944</t>
+  </si>
+  <si>
+    <t>LP-047510</t>
+  </si>
+  <si>
+    <t>LP-047878</t>
+  </si>
+  <si>
+    <t>LP-047992</t>
+  </si>
+  <si>
+    <t>LP-048031</t>
+  </si>
+  <si>
+    <t>LP-048384</t>
+  </si>
+  <si>
+    <t>LP-048997</t>
+  </si>
+  <si>
+    <t>LP-049036</t>
+  </si>
+  <si>
+    <t>LP-049117</t>
+  </si>
+  <si>
+    <t>LP-049167</t>
+  </si>
+  <si>
+    <t>LP-049175</t>
+  </si>
+  <si>
+    <t>LP-049217</t>
+  </si>
+  <si>
+    <t>LP-049368</t>
+  </si>
+  <si>
+    <t>LP-049376</t>
+  </si>
+  <si>
+    <t>LP-049504</t>
+  </si>
+  <si>
+    <t>LP-049508</t>
+  </si>
+  <si>
+    <t>LP-049715</t>
+  </si>
+  <si>
+    <t>LP-049958</t>
+  </si>
+  <si>
+    <t>LP-049959</t>
+  </si>
+  <si>
+    <t>LP-049960</t>
+  </si>
+  <si>
+    <t>LP-049962</t>
+  </si>
+  <si>
+    <t>LP-049964</t>
+  </si>
+  <si>
+    <t>LP-049965</t>
+  </si>
+  <si>
+    <t>LP-049972</t>
+  </si>
+  <si>
+    <t>LP-050129</t>
+  </si>
+  <si>
+    <t>LP-050177</t>
+  </si>
+  <si>
+    <t>LP-050234</t>
+  </si>
+  <si>
+    <t>LP-050254</t>
+  </si>
+  <si>
+    <t>LP-050400</t>
+  </si>
+  <si>
+    <t>LP-050654</t>
+  </si>
+  <si>
+    <t>LP-050666</t>
+  </si>
+  <si>
+    <t>LP-050668</t>
+  </si>
+  <si>
+    <t>LP-050723</t>
+  </si>
+  <si>
+    <t>LP-033372</t>
+  </si>
+  <si>
+    <t>LP-044444</t>
+  </si>
+  <si>
+    <t>LP-046043</t>
+  </si>
+  <si>
+    <t>LP-046044</t>
+  </si>
+  <si>
+    <t>LP-046692</t>
+  </si>
+  <si>
+    <t>LP-047416</t>
+  </si>
+  <si>
+    <t>LP-047460</t>
+  </si>
+  <si>
+    <t>LP-047461</t>
+  </si>
+  <si>
+    <t>LP-047462</t>
+  </si>
+  <si>
+    <t>LP-047463</t>
+  </si>
+  <si>
+    <t>LP-047766</t>
+  </si>
+  <si>
+    <t>LP-047954</t>
+  </si>
+  <si>
+    <t>LP-048009</t>
+  </si>
+  <si>
+    <t>LP-048020</t>
+  </si>
+  <si>
+    <t>LP-048099</t>
+  </si>
+  <si>
+    <t>LP-048353</t>
+  </si>
+  <si>
+    <t>LP-048355</t>
+  </si>
+  <si>
+    <t>LP-048356</t>
+  </si>
+  <si>
+    <t>LP-048468</t>
+  </si>
+  <si>
+    <t>LP-048474</t>
+  </si>
+  <si>
+    <t>LP-048699</t>
+  </si>
+  <si>
+    <t>LP-048851</t>
+  </si>
+  <si>
+    <t>LP-049053</t>
+  </si>
+  <si>
+    <t>LP-049067</t>
+  </si>
+  <si>
+    <t>LP-049104</t>
+  </si>
+  <si>
+    <t>LP-049303</t>
+  </si>
+  <si>
+    <t>LP-049403</t>
+  </si>
+  <si>
+    <t>LP-049412</t>
+  </si>
+  <si>
+    <t>LP-049429</t>
+  </si>
+  <si>
+    <t>LP-049430</t>
+  </si>
+  <si>
+    <t>LP-049483</t>
+  </si>
+  <si>
+    <t>LP-049655</t>
+  </si>
+  <si>
+    <t>LP-049716</t>
+  </si>
+  <si>
+    <t>LP-049783</t>
+  </si>
+  <si>
+    <t>LP-049784</t>
+  </si>
+  <si>
+    <t>LP-049809</t>
+  </si>
+  <si>
+    <t>LP-049923</t>
+  </si>
+  <si>
+    <t>LP-049983</t>
+  </si>
+  <si>
+    <t>LP-050006</t>
+  </si>
+  <si>
+    <t>LP-050008</t>
+  </si>
+  <si>
+    <t>LP-050014</t>
+  </si>
+  <si>
+    <t>LP-050052</t>
+  </si>
+  <si>
+    <t>LP-050073</t>
+  </si>
+  <si>
+    <t>LP-050110</t>
+  </si>
+  <si>
+    <t>LP-050164</t>
+  </si>
+  <si>
+    <t>LP-050207</t>
+  </si>
+  <si>
+    <t>LP-050290</t>
+  </si>
+  <si>
+    <t>LP-050297</t>
+  </si>
+  <si>
+    <t>LP-050315</t>
+  </si>
+  <si>
+    <t>LP-050332</t>
+  </si>
+  <si>
+    <t>LP-050342</t>
+  </si>
+  <si>
+    <t>LP-050338</t>
+  </si>
+  <si>
+    <t>LP-050358</t>
+  </si>
+  <si>
+    <t>LP-050374</t>
+  </si>
+  <si>
+    <t>LP-050483</t>
+  </si>
+  <si>
+    <t>LP-050490</t>
+  </si>
+  <si>
+    <t>LP-050502</t>
+  </si>
+  <si>
+    <t>LP-050541</t>
+  </si>
+  <si>
+    <t>LP-050555</t>
+  </si>
+  <si>
+    <t>LP-050594</t>
+  </si>
+  <si>
+    <t>LP-050611</t>
+  </si>
+  <si>
+    <t>LP-050619</t>
+  </si>
+  <si>
+    <t>LP-050625</t>
+  </si>
+  <si>
+    <t>LP-050636</t>
+  </si>
+  <si>
+    <t>LP-050637</t>
+  </si>
+  <si>
+    <t>LP-050694</t>
+  </si>
+  <si>
+    <t>LP-050698</t>
+  </si>
+  <si>
+    <t>LP-050705</t>
+  </si>
+  <si>
+    <t>LP-050728</t>
+  </si>
+  <si>
+    <t>LP-050838</t>
+  </si>
+  <si>
+    <t>LP-050841</t>
+  </si>
+  <si>
+    <t>LP-050884</t>
+  </si>
+  <si>
+    <t>LP-050897</t>
+  </si>
+  <si>
+    <t>LP-050398</t>
+  </si>
+  <si>
+    <t>LP-050940</t>
+  </si>
+  <si>
+    <t>LP-051005</t>
+  </si>
+  <si>
+    <t>LP-051124</t>
+  </si>
+  <si>
+    <t>LP-051125</t>
+  </si>
+  <si>
+    <t>LP-051211</t>
+  </si>
+  <si>
+    <t>LP-051247</t>
   </si>
 </sst>
 </file>
@@ -448,11 +730,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -467,152 +749,570 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0BAE638-FB60-412B-BE34-99AE534D1BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F37BB4-977B-4815-82CF-F4DD09FE7FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>LP</t>
   </si>
@@ -31,127 +31,415 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-047878</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
-  </si>
-  <si>
-    <t>LP-049715</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-050666</t>
-  </si>
-  <si>
-    <t>LP-050668</t>
-  </si>
-  <si>
-    <t>LP-033372</t>
-  </si>
-  <si>
-    <t>LP-044444</t>
-  </si>
-  <si>
-    <t>LP-047416</t>
-  </si>
-  <si>
-    <t>LP-047766</t>
-  </si>
-  <si>
-    <t>LP-047954</t>
-  </si>
-  <si>
-    <t>LP-048009</t>
-  </si>
-  <si>
-    <t>LP-048099</t>
-  </si>
-  <si>
-    <t>LP-048353</t>
-  </si>
-  <si>
-    <t>LP-048468</t>
-  </si>
-  <si>
-    <t>LP-049483</t>
-  </si>
-  <si>
-    <t>LP-049716</t>
-  </si>
-  <si>
-    <t>LP-049784</t>
-  </si>
-  <si>
-    <t>LP-050110</t>
-  </si>
-  <si>
-    <t>LP-050374</t>
-  </si>
-  <si>
-    <t>LP-050483</t>
-  </si>
-  <si>
-    <t>LP-050490</t>
-  </si>
-  <si>
-    <t>LP-050502</t>
-  </si>
-  <si>
-    <t>LP-050541</t>
-  </si>
-  <si>
-    <t>LP-050555</t>
-  </si>
-  <si>
-    <t>LP-050594</t>
-  </si>
-  <si>
-    <t>LP-050619</t>
-  </si>
-  <si>
-    <t>LP-050625</t>
-  </si>
-  <si>
-    <t>LP-050636</t>
-  </si>
-  <si>
-    <t>LP-050637</t>
-  </si>
-  <si>
-    <t>LP-050694</t>
-  </si>
-  <si>
-    <t>LP-050698</t>
-  </si>
-  <si>
-    <t>LP-050705</t>
-  </si>
-  <si>
-    <t>LP-050728</t>
-  </si>
-  <si>
-    <t>LP-050838</t>
-  </si>
-  <si>
-    <t>LP-050884</t>
-  </si>
-  <si>
-    <t>LP-050897</t>
-  </si>
-  <si>
-    <t>LP-050940</t>
-  </si>
-  <si>
-    <t>LP-051124</t>
-  </si>
-  <si>
-    <t>LP-051125</t>
-  </si>
-  <si>
-    <t>LP-051211</t>
+    <t>LP-042414</t>
+  </si>
+  <si>
+    <t>LP-042416</t>
+  </si>
+  <si>
+    <t>LP-043549</t>
+  </si>
+  <si>
+    <t>LP-044901</t>
+  </si>
+  <si>
+    <t>LP-045346</t>
+  </si>
+  <si>
+    <t>LP-045347</t>
+  </si>
+  <si>
+    <t>LP-046170</t>
+  </si>
+  <si>
+    <t>LP-046338</t>
+  </si>
+  <si>
+    <t>LP-046931</t>
+  </si>
+  <si>
+    <t>LP-047284</t>
+  </si>
+  <si>
+    <t>LP-047334</t>
+  </si>
+  <si>
+    <t>LP-047479</t>
+  </si>
+  <si>
+    <t>LP-047643</t>
+  </si>
+  <si>
+    <t>LP-048273</t>
+  </si>
+  <si>
+    <t>LP-048754</t>
+  </si>
+  <si>
+    <t>LP-048767</t>
+  </si>
+  <si>
+    <t>LP-048979</t>
+  </si>
+  <si>
+    <t>LP-048986</t>
+  </si>
+  <si>
+    <t>LP-049314</t>
+  </si>
+  <si>
+    <t>LP-049327</t>
+  </si>
+  <si>
+    <t>LP-049331</t>
+  </si>
+  <si>
+    <t>LP-049337</t>
+  </si>
+  <si>
+    <t>LP-049360</t>
+  </si>
+  <si>
+    <t>LP-049361</t>
+  </si>
+  <si>
+    <t>LP-049378</t>
+  </si>
+  <si>
+    <t>LP-049379</t>
+  </si>
+  <si>
+    <t>LP-049385</t>
+  </si>
+  <si>
+    <t>LP-049392</t>
+  </si>
+  <si>
+    <t>LP-049393</t>
+  </si>
+  <si>
+    <t>LP-049661</t>
+  </si>
+  <si>
+    <t>LP-049662</t>
+  </si>
+  <si>
+    <t>LP-049689</t>
+  </si>
+  <si>
+    <t>LP-049777</t>
+  </si>
+  <si>
+    <t>LP-049849</t>
+  </si>
+  <si>
+    <t>LP-049957</t>
+  </si>
+  <si>
+    <t>LP-049961</t>
+  </si>
+  <si>
+    <t>LP-049967</t>
+  </si>
+  <si>
+    <t>LP-049994</t>
+  </si>
+  <si>
+    <t>LP-050130</t>
+  </si>
+  <si>
+    <t>LP-050141</t>
+  </si>
+  <si>
+    <t>LP-050144</t>
+  </si>
+  <si>
+    <t>LP-050154</t>
+  </si>
+  <si>
+    <t>LP-050232</t>
+  </si>
+  <si>
+    <t>LP-050241</t>
+  </si>
+  <si>
+    <t>LP-050435</t>
+  </si>
+  <si>
+    <t>LP-050463</t>
+  </si>
+  <si>
+    <t>LP-050464</t>
+  </si>
+  <si>
+    <t>LP-050715</t>
+  </si>
+  <si>
+    <t>LP-050716</t>
+  </si>
+  <si>
+    <t>LP-050759</t>
+  </si>
+  <si>
+    <t>LP-050864</t>
+  </si>
+  <si>
+    <t>LP-050979</t>
+  </si>
+  <si>
+    <t>LP-043816</t>
+  </si>
+  <si>
+    <t>LP-045946</t>
+  </si>
+  <si>
+    <t>LP-046294</t>
+  </si>
+  <si>
+    <t>LP-046869</t>
+  </si>
+  <si>
+    <t>LP-046870</t>
+  </si>
+  <si>
+    <t>LP-047083</t>
+  </si>
+  <si>
+    <t>LP-047208</t>
+  </si>
+  <si>
+    <t>LP-047290</t>
+  </si>
+  <si>
+    <t>LP-047455</t>
+  </si>
+  <si>
+    <t>LP-047458</t>
+  </si>
+  <si>
+    <t>LP-047466</t>
+  </si>
+  <si>
+    <t>LP-047762</t>
+  </si>
+  <si>
+    <t>LP-047763</t>
+  </si>
+  <si>
+    <t>LP-047769</t>
+  </si>
+  <si>
+    <t>LP-047852</t>
+  </si>
+  <si>
+    <t>LP-047928</t>
+  </si>
+  <si>
+    <t>LP-047968</t>
+  </si>
+  <si>
+    <t>LP-048006</t>
+  </si>
+  <si>
+    <t>LP-048320</t>
+  </si>
+  <si>
+    <t>LP-048467</t>
+  </si>
+  <si>
+    <t>LP-048471</t>
+  </si>
+  <si>
+    <t>LP-048473</t>
+  </si>
+  <si>
+    <t>LP-048579</t>
+  </si>
+  <si>
+    <t>LP-048598</t>
+  </si>
+  <si>
+    <t>LP-048599</t>
+  </si>
+  <si>
+    <t>LP-048600</t>
+  </si>
+  <si>
+    <t>LP-048601</t>
+  </si>
+  <si>
+    <t>LP-048603</t>
+  </si>
+  <si>
+    <t>LP-048605</t>
+  </si>
+  <si>
+    <t>LP-048606</t>
+  </si>
+  <si>
+    <t>LP-048664</t>
+  </si>
+  <si>
+    <t>LP-048666</t>
+  </si>
+  <si>
+    <t>LP-048700</t>
+  </si>
+  <si>
+    <t>LP-048909</t>
+  </si>
+  <si>
+    <t>LP-048910</t>
+  </si>
+  <si>
+    <t>LP-048912</t>
+  </si>
+  <si>
+    <t>LP-048913</t>
+  </si>
+  <si>
+    <t>LP-048914</t>
+  </si>
+  <si>
+    <t>LP-049023</t>
+  </si>
+  <si>
+    <t>LP-049081</t>
+  </si>
+  <si>
+    <t>LP-049366</t>
+  </si>
+  <si>
+    <t>LP-049438</t>
+  </si>
+  <si>
+    <t>LP-049497</t>
+  </si>
+  <si>
+    <t>LP-049827</t>
+  </si>
+  <si>
+    <t>LP-049982</t>
+  </si>
+  <si>
+    <t>LP-049984</t>
+  </si>
+  <si>
+    <t>LP-049985</t>
+  </si>
+  <si>
+    <t>LP-050017</t>
+  </si>
+  <si>
+    <t>LP-050108</t>
+  </si>
+  <si>
+    <t>LP-050109</t>
+  </si>
+  <si>
+    <t>LP-050226</t>
+  </si>
+  <si>
+    <t>LP-050239</t>
+  </si>
+  <si>
+    <t>LP-050264</t>
+  </si>
+  <si>
+    <t>LP-050318</t>
+  </si>
+  <si>
+    <t>LP-050355</t>
+  </si>
+  <si>
+    <t>LP-050371</t>
+  </si>
+  <si>
+    <t>LP-050372</t>
+  </si>
+  <si>
+    <t>LP-050413</t>
+  </si>
+  <si>
+    <t>LP-050434</t>
+  </si>
+  <si>
+    <t>LP-050485</t>
+  </si>
+  <si>
+    <t>LP-050493</t>
+  </si>
+  <si>
+    <t>LP-050496</t>
+  </si>
+  <si>
+    <t>LP-050572</t>
+  </si>
+  <si>
+    <t>LP-050573</t>
+  </si>
+  <si>
+    <t>LP-050584</t>
+  </si>
+  <si>
+    <t>LP-050597</t>
+  </si>
+  <si>
+    <t>LP-050634</t>
+  </si>
+  <si>
+    <t>LP-050659</t>
+  </si>
+  <si>
+    <t>LP-050691</t>
+  </si>
+  <si>
+    <t>LP-050692</t>
+  </si>
+  <si>
+    <t>LP-050701</t>
+  </si>
+  <si>
+    <t>LP-050725</t>
+  </si>
+  <si>
+    <t>LP-050831</t>
+  </si>
+  <si>
+    <t>LP-050832</t>
+  </si>
+  <si>
+    <t>LP-050833</t>
+  </si>
+  <si>
+    <t>LP-050879</t>
+  </si>
+  <si>
+    <t>LP-050880</t>
+  </si>
+  <si>
+    <t>LP-050908</t>
+  </si>
+  <si>
+    <t>LP-050914</t>
+  </si>
+  <si>
+    <t>LP-050953</t>
+  </si>
+  <si>
+    <t>LP-050955</t>
+  </si>
+  <si>
+    <t>LP-051131</t>
+  </si>
+  <si>
+    <t>LP-051185</t>
+  </si>
+  <si>
+    <t>LP-051268</t>
+  </si>
+  <si>
+    <t>LP-051550</t>
   </si>
 </sst>
 </file>
@@ -514,11 +802,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -533,312 +821,685 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B21" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B22" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B29" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B32" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>36</v>
       </c>
-      <c r="B34" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>39</v>
       </c>
-      <c r="B37" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>42</v>
       </c>
-      <c r="B40" t="s">
-        <v>5</v>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B5DC97-1F6A-40DA-9C9B-FE11D31F744B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B4DFEF-0446-4358-A313-ECCFC8B0CE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
   <si>
     <t>LP</t>
   </si>
@@ -31,175 +31,349 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-049662</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-049689</t>
-  </si>
-  <si>
-    <t>LP-050130</t>
-  </si>
-  <si>
-    <t>LP-050141</t>
-  </si>
-  <si>
-    <t>LP-050716</t>
-  </si>
-  <si>
-    <t>LP-050759</t>
-  </si>
-  <si>
-    <t>LP-050864</t>
-  </si>
-  <si>
-    <t>LP-046294</t>
-  </si>
-  <si>
-    <t>LP-047455</t>
-  </si>
-  <si>
-    <t>LP-047458</t>
-  </si>
-  <si>
-    <t>LP-047466</t>
-  </si>
-  <si>
-    <t>LP-047762</t>
-  </si>
-  <si>
-    <t>LP-047763</t>
-  </si>
-  <si>
-    <t>LP-047769</t>
-  </si>
-  <si>
-    <t>LP-047852</t>
-  </si>
-  <si>
-    <t>LP-047968</t>
-  </si>
-  <si>
-    <t>LP-048006</t>
-  </si>
-  <si>
-    <t>LP-048320</t>
-  </si>
-  <si>
-    <t>LP-048467</t>
-  </si>
-  <si>
-    <t>LP-048471</t>
-  </si>
-  <si>
-    <t>LP-048473</t>
-  </si>
-  <si>
-    <t>LP-048579</t>
-  </si>
-  <si>
-    <t>LP-048603</t>
-  </si>
-  <si>
-    <t>LP-048605</t>
-  </si>
-  <si>
-    <t>LP-048606</t>
-  </si>
-  <si>
-    <t>LP-048909</t>
-  </si>
-  <si>
-    <t>LP-048910</t>
-  </si>
-  <si>
-    <t>LP-048912</t>
-  </si>
-  <si>
-    <t>LP-048913</t>
-  </si>
-  <si>
-    <t>LP-048914</t>
-  </si>
-  <si>
-    <t>LP-049023</t>
-  </si>
-  <si>
-    <t>Possui linhas de compra e apontamento!</t>
-  </si>
-  <si>
-    <t>LP-049982</t>
-  </si>
-  <si>
-    <t>LP-049984</t>
-  </si>
-  <si>
-    <t>LP-049985</t>
-  </si>
-  <si>
-    <t>LP-050264</t>
-  </si>
-  <si>
-    <t>LP-050371</t>
-  </si>
-  <si>
-    <t>LP-050372</t>
-  </si>
-  <si>
-    <t>LP-050485</t>
-  </si>
-  <si>
-    <t>LP-050496</t>
-  </si>
-  <si>
-    <t>LP-050572</t>
-  </si>
-  <si>
-    <t>LP-050597</t>
-  </si>
-  <si>
-    <t>LP-050634</t>
-  </si>
-  <si>
-    <t>LP-050691</t>
-  </si>
-  <si>
-    <t>LP-050692</t>
-  </si>
-  <si>
-    <t>LP-050701</t>
-  </si>
-  <si>
-    <t>LP-050831</t>
-  </si>
-  <si>
-    <t>LP-050832</t>
-  </si>
-  <si>
-    <t>LP-050833</t>
-  </si>
-  <si>
-    <t>LP-050879</t>
-  </si>
-  <si>
-    <t>LP-050880</t>
-  </si>
-  <si>
-    <t>LP-050908</t>
-  </si>
-  <si>
-    <t>LP-050914</t>
-  </si>
-  <si>
-    <t>LP-050955</t>
-  </si>
-  <si>
-    <t>LP-051131</t>
-  </si>
-  <si>
-    <t>LP-051185</t>
+    <t>LP-049093</t>
+  </si>
+  <si>
+    <t>LP-049293</t>
+  </si>
+  <si>
+    <t>LP-049297</t>
+  </si>
+  <si>
+    <t>LP-049300</t>
+  </si>
+  <si>
+    <t>LP-049245</t>
+  </si>
+  <si>
+    <t>LP-050020</t>
+  </si>
+  <si>
+    <t>LP-049851</t>
+  </si>
+  <si>
+    <t>LP-043711</t>
+  </si>
+  <si>
+    <t>LP-045965</t>
+  </si>
+  <si>
+    <t>LP-047168</t>
+  </si>
+  <si>
+    <t>LP-047418</t>
+  </si>
+  <si>
+    <t>LP-047956</t>
+  </si>
+  <si>
+    <t>LP-047564</t>
+  </si>
+  <si>
+    <t>LP-048980</t>
+  </si>
+  <si>
+    <t>LP-049043</t>
+  </si>
+  <si>
+    <t>LP-048670</t>
+  </si>
+  <si>
+    <t>LP-048900</t>
+  </si>
+  <si>
+    <t>LP-049042</t>
+  </si>
+  <si>
+    <t>LP-049048</t>
+  </si>
+  <si>
+    <t>LP-049115</t>
+  </si>
+  <si>
+    <t>LP-045420</t>
+  </si>
+  <si>
+    <t>LP-049260</t>
+  </si>
+  <si>
+    <t>LP-049410</t>
+  </si>
+  <si>
+    <t>LP-049550</t>
+  </si>
+  <si>
+    <t>LP-050004</t>
+  </si>
+  <si>
+    <t>LP-050504</t>
+  </si>
+  <si>
+    <t>LP-049044</t>
+  </si>
+  <si>
+    <t>LP-050887</t>
+  </si>
+  <si>
+    <t>LP-050445</t>
+  </si>
+  <si>
+    <t>LP-049701</t>
+  </si>
+  <si>
+    <t>LP-049802</t>
+  </si>
+  <si>
+    <t>LP-049808</t>
+  </si>
+  <si>
+    <t>LP-049869</t>
+  </si>
+  <si>
+    <t>LP-050558</t>
+  </si>
+  <si>
+    <t>LP-050559</t>
+  </si>
+  <si>
+    <t>LP-050843</t>
+  </si>
+  <si>
+    <t>LP-049686</t>
+  </si>
+  <si>
+    <t>LP-049692</t>
+  </si>
+  <si>
+    <t>LP-049935</t>
+  </si>
+  <si>
+    <t>LP-050034</t>
+  </si>
+  <si>
+    <t>LP-050035</t>
+  </si>
+  <si>
+    <t>LP-050229</t>
+  </si>
+  <si>
+    <t>LP-050235</t>
+  </si>
+  <si>
+    <t>LP-050275</t>
+  </si>
+  <si>
+    <t>LP-047413</t>
+  </si>
+  <si>
+    <t>LP-048076</t>
+  </si>
+  <si>
+    <t>LP-048588</t>
+  </si>
+  <si>
+    <t>LP-049068</t>
+  </si>
+  <si>
+    <t>LP-049778</t>
+  </si>
+  <si>
+    <t>LP-049894</t>
+  </si>
+  <si>
+    <t>LP-050677</t>
+  </si>
+  <si>
+    <t>LP-050495</t>
+  </si>
+  <si>
+    <t>LP-050497</t>
+  </si>
+  <si>
+    <t>LP-050499</t>
+  </si>
+  <si>
+    <t>LP-050809</t>
+  </si>
+  <si>
+    <t>LP-050846</t>
+  </si>
+  <si>
+    <t>LP-050885</t>
+  </si>
+  <si>
+    <t>LP-041331</t>
+  </si>
+  <si>
+    <t>LP-047546</t>
+  </si>
+  <si>
+    <t>LP-047961</t>
+  </si>
+  <si>
+    <t>LP-047994</t>
+  </si>
+  <si>
+    <t>LP-048234</t>
+  </si>
+  <si>
+    <t>LP-048235</t>
+  </si>
+  <si>
+    <t>LP-048446</t>
+  </si>
+  <si>
+    <t>LP-048460</t>
+  </si>
+  <si>
+    <t>LP-049797</t>
+  </si>
+  <si>
+    <t>LP-050500</t>
+  </si>
+  <si>
+    <t>LP-050530</t>
+  </si>
+  <si>
+    <t>LP-050556</t>
+  </si>
+  <si>
+    <t>LP-050580</t>
+  </si>
+  <si>
+    <t>LP-050618</t>
+  </si>
+  <si>
+    <t>LP-050700</t>
+  </si>
+  <si>
+    <t>LP-050799</t>
+  </si>
+  <si>
+    <t>LP-050800</t>
+  </si>
+  <si>
+    <t>LP-050876</t>
+  </si>
+  <si>
+    <t>LP-051058</t>
+  </si>
+  <si>
+    <t>LP-049715</t>
+  </si>
+  <si>
+    <t>LP-050666</t>
+  </si>
+  <si>
+    <t>LP-050668</t>
+  </si>
+  <si>
+    <t>LP-033372</t>
+  </si>
+  <si>
+    <t>LP-044444</t>
+  </si>
+  <si>
+    <t>LP-047416</t>
+  </si>
+  <si>
+    <t>LP-047766</t>
+  </si>
+  <si>
+    <t>LP-047954</t>
+  </si>
+  <si>
+    <t>LP-048009</t>
+  </si>
+  <si>
+    <t>LP-048099</t>
+  </si>
+  <si>
+    <t>LP-048353</t>
+  </si>
+  <si>
+    <t>LP-048468</t>
+  </si>
+  <si>
+    <t>LP-049483</t>
+  </si>
+  <si>
+    <t>LP-049716</t>
+  </si>
+  <si>
+    <t>LP-049784</t>
+  </si>
+  <si>
+    <t>LP-050110</t>
+  </si>
+  <si>
+    <t>LP-050374</t>
+  </si>
+  <si>
+    <t>LP-050483</t>
+  </si>
+  <si>
+    <t>LP-050490</t>
+  </si>
+  <si>
+    <t>LP-050502</t>
+  </si>
+  <si>
+    <t>LP-050541</t>
+  </si>
+  <si>
+    <t>LP-050555</t>
+  </si>
+  <si>
+    <t>LP-050594</t>
+  </si>
+  <si>
+    <t>LP-050619</t>
+  </si>
+  <si>
+    <t>LP-050625</t>
+  </si>
+  <si>
+    <t>LP-050636</t>
+  </si>
+  <si>
+    <t>LP-050637</t>
+  </si>
+  <si>
+    <t>LP-050694</t>
+  </si>
+  <si>
+    <t>LP-050698</t>
+  </si>
+  <si>
+    <t>LP-050705</t>
+  </si>
+  <si>
+    <t>LP-050728</t>
+  </si>
+  <si>
+    <t>LP-050838</t>
+  </si>
+  <si>
+    <t>LP-050884</t>
+  </si>
+  <si>
+    <t>LP-050897</t>
+  </si>
+  <si>
+    <t>LP-050940</t>
+  </si>
+  <si>
+    <t>LP-051124</t>
+  </si>
+  <si>
+    <t>LP-051125</t>
+  </si>
+  <si>
+    <t>LP-051211</t>
+  </si>
+  <si>
+    <t>LP-051342</t>
   </si>
 </sst>
 </file>
@@ -562,11 +736,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -581,440 +755,615 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>30</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>31</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>33</v>
       </c>
-      <c r="B32" t="s">
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>36</v>
       </c>
-      <c r="B34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>37</v>
       </c>
-      <c r="B35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>39</v>
       </c>
-      <c r="B37" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>41</v>
       </c>
-      <c r="B39" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>42</v>
       </c>
-      <c r="B40" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>43</v>
       </c>
-      <c r="B41" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>44</v>
       </c>
-      <c r="B42" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>45</v>
       </c>
-      <c r="B43" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>46</v>
       </c>
-      <c r="B44" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>47</v>
       </c>
-      <c r="B45" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>48</v>
       </c>
-      <c r="B46" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>49</v>
       </c>
-      <c r="B47" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
         <v>50</v>
       </c>
-      <c r="B48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>51</v>
       </c>
-      <c r="B49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>52</v>
       </c>
-      <c r="B50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
         <v>53</v>
       </c>
-      <c r="B51" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>54</v>
       </c>
-      <c r="B52" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>55</v>
       </c>
-      <c r="B53" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>56</v>
       </c>
-      <c r="B54" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>57</v>
       </c>
-      <c r="B55" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>58</v>
       </c>
-      <c r="B56" t="s">
-        <v>3</v>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B4DFEF-0446-4358-A313-ECCFC8B0CE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C000998-0B96-4DCF-8774-C5A27462A05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$118</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
   <si>
     <t>LP</t>
   </si>
@@ -31,22 +31,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-049093</t>
-  </si>
-  <si>
-    <t>LP-049293</t>
-  </si>
-  <si>
-    <t>LP-049297</t>
-  </si>
-  <si>
-    <t>LP-049300</t>
-  </si>
-  <si>
     <t>LP-049245</t>
   </si>
   <si>
-    <t>LP-050020</t>
+    <t>Compromisso pendente!</t>
   </si>
   <si>
     <t>LP-049851</t>
@@ -67,13 +55,13 @@
     <t>LP-047956</t>
   </si>
   <si>
+    <t>Possui linhas de compra e apontamento!</t>
+  </si>
+  <si>
     <t>LP-047564</t>
   </si>
   <si>
     <t>LP-048980</t>
-  </si>
-  <si>
-    <t>LP-049043</t>
   </si>
   <si>
     <t>LP-048670</t>
@@ -736,11 +724,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B124"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -755,615 +743,612 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>44</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C000998-0B96-4DCF-8774-C5A27462A05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7473036-ED86-41FB-A901-C30B7611D227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$108</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
   <si>
     <t>LP</t>
   </si>
@@ -64,21 +64,6 @@
     <t>LP-048980</t>
   </si>
   <si>
-    <t>LP-048670</t>
-  </si>
-  <si>
-    <t>LP-048900</t>
-  </si>
-  <si>
-    <t>LP-049042</t>
-  </si>
-  <si>
-    <t>LP-049048</t>
-  </si>
-  <si>
-    <t>LP-049115</t>
-  </si>
-  <si>
     <t>LP-045420</t>
   </si>
   <si>
@@ -91,19 +76,10 @@
     <t>LP-049550</t>
   </si>
   <si>
-    <t>LP-050004</t>
-  </si>
-  <si>
     <t>LP-050504</t>
   </si>
   <si>
-    <t>LP-049044</t>
-  </si>
-  <si>
     <t>LP-050887</t>
-  </si>
-  <si>
-    <t>LP-050445</t>
   </si>
   <si>
     <t>LP-049701</t>
@@ -724,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -815,540 +791,538 @@
       <c r="A11" t="s">
         <v>13</v>
       </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4543F532-AD92-4AB8-BE73-D804383E03F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF63D87-8383-467B-A0CA-9859EA6EBC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$58</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>LP</t>
   </si>
@@ -28,211 +31,91 @@
     <t>Status</t>
   </si>
   <si>
+    <t>LP-049934</t>
+  </si>
+  <si>
+    <t>Compromisso pendente!</t>
+  </si>
+  <si>
+    <t>LP-050376</t>
+  </si>
+  <si>
+    <t>LP-050670</t>
+  </si>
+  <si>
+    <t>LP-050714</t>
+  </si>
+  <si>
+    <t>LP-050732</t>
+  </si>
+  <si>
+    <t>LP-050733</t>
+  </si>
+  <si>
+    <t>LP-050734</t>
+  </si>
+  <si>
+    <t>LP-050754</t>
+  </si>
+  <si>
+    <t>LP-050857</t>
+  </si>
+  <si>
+    <t>LP-050894</t>
+  </si>
+  <si>
+    <t>LP-047955</t>
+  </si>
+  <si>
+    <t>LP-047964</t>
+  </si>
+  <si>
+    <t>LP-047987</t>
+  </si>
+  <si>
+    <t>LP-047970</t>
+  </si>
+  <si>
+    <t>LP-048026</t>
+  </si>
+  <si>
+    <t>LP-048427</t>
+  </si>
+  <si>
+    <t>LP-048441</t>
+  </si>
+  <si>
+    <t>LP-048472</t>
+  </si>
+  <si>
+    <t>LP-048580</t>
+  </si>
+  <si>
+    <t>LP-048640</t>
+  </si>
+  <si>
+    <t>LP-048641</t>
+  </si>
+  <si>
+    <t>LP-049056</t>
+  </si>
+  <si>
+    <t>LP-049092</t>
+  </si>
+  <si>
+    <t>LP-049482</t>
+  </si>
+  <si>
+    <t>LP-049513</t>
+  </si>
+  <si>
+    <t>LP-049657</t>
+  </si>
+  <si>
+    <t>LP-049714</t>
+  </si>
+  <si>
     <t>LP-049716</t>
-  </si>
-  <si>
-    <t>LP-046342</t>
-  </si>
-  <si>
-    <t>LP-046346</t>
-  </si>
-  <si>
-    <t>LP-046957</t>
-  </si>
-  <si>
-    <t>LP-048167</t>
-  </si>
-  <si>
-    <t>LP-048749</t>
-  </si>
-  <si>
-    <t>LP-048975</t>
-  </si>
-  <si>
-    <t>LP-049118</t>
-  </si>
-  <si>
-    <t>LP-049173</t>
-  </si>
-  <si>
-    <t>LP-049344</t>
-  </si>
-  <si>
-    <t>LP-049353</t>
-  </si>
-  <si>
-    <t>LP-049357</t>
-  </si>
-  <si>
-    <t>LP-049358</t>
-  </si>
-  <si>
-    <t>LP-049364</t>
-  </si>
-  <si>
-    <t>LP-049387</t>
-  </si>
-  <si>
-    <t>LP-049518</t>
-  </si>
-  <si>
-    <t>LP-049648</t>
-  </si>
-  <si>
-    <t>LP-049669</t>
-  </si>
-  <si>
-    <t>LP-049765</t>
-  </si>
-  <si>
-    <t>LP-049842</t>
-  </si>
-  <si>
-    <t>LP-049848</t>
-  </si>
-  <si>
-    <t>LP-049934</t>
-  </si>
-  <si>
-    <t>LP-050086</t>
-  </si>
-  <si>
-    <t>LP-050131</t>
-  </si>
-  <si>
-    <t>LP-050159</t>
-  </si>
-  <si>
-    <t>LP-050160</t>
-  </si>
-  <si>
-    <t>LP-050376</t>
-  </si>
-  <si>
-    <t>LP-050382</t>
-  </si>
-  <si>
-    <t>LP-050383</t>
-  </si>
-  <si>
-    <t>LP-050389</t>
-  </si>
-  <si>
-    <t>LP-050392</t>
-  </si>
-  <si>
-    <t>LP-050428</t>
-  </si>
-  <si>
-    <t>LP-050518</t>
-  </si>
-  <si>
-    <t>LP-050519</t>
-  </si>
-  <si>
-    <t>LP-050670</t>
-  </si>
-  <si>
-    <t>LP-050714</t>
-  </si>
-  <si>
-    <t>LP-050722</t>
-  </si>
-  <si>
-    <t>LP-050732</t>
-  </si>
-  <si>
-    <t>LP-050733</t>
-  </si>
-  <si>
-    <t>LP-050734</t>
-  </si>
-  <si>
-    <t>LP-050754</t>
-  </si>
-  <si>
-    <t>LP-050857</t>
-  </si>
-  <si>
-    <t>LP-050894</t>
-  </si>
-  <si>
-    <t>LP-044555</t>
-  </si>
-  <si>
-    <t>LP-044804</t>
-  </si>
-  <si>
-    <t>LP-046037</t>
-  </si>
-  <si>
-    <t>LP-047277</t>
-  </si>
-  <si>
-    <t>LP-047286</t>
-  </si>
-  <si>
-    <t>LP-047620</t>
-  </si>
-  <si>
-    <t>LP-047709</t>
-  </si>
-  <si>
-    <t>LP-047955</t>
-  </si>
-  <si>
-    <t>LP-047964</t>
-  </si>
-  <si>
-    <t>LP-047987</t>
-  </si>
-  <si>
-    <t>LP-047970</t>
-  </si>
-  <si>
-    <t>LP-048026</t>
-  </si>
-  <si>
-    <t>LP-048350</t>
-  </si>
-  <si>
-    <t>LP-048383</t>
-  </si>
-  <si>
-    <t>LP-048427</t>
-  </si>
-  <si>
-    <t>LP-048441</t>
-  </si>
-  <si>
-    <t>LP-048472</t>
-  </si>
-  <si>
-    <t>LP-048580</t>
-  </si>
-  <si>
-    <t>LP-048640</t>
-  </si>
-  <si>
-    <t>LP-048641</t>
-  </si>
-  <si>
-    <t>LP-049056</t>
-  </si>
-  <si>
-    <t>LP-049092</t>
-  </si>
-  <si>
-    <t>LP-049482</t>
-  </si>
-  <si>
-    <t>LP-049513</t>
-  </si>
-  <si>
-    <t>LP-049657</t>
-  </si>
-  <si>
-    <t>LP-049714</t>
   </si>
   <si>
     <t>LP-049888</t>
@@ -676,11 +559,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -693,6 +576,9 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -700,485 +586,325 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
+      <c r="B8" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
+      <c r="B9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
+      <c r="B10" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
+      <c r="B12" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FF63D87-8383-467B-A0CA-9859EA6EBC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E58338-FE9A-4BB8-98AB-E6B221AA88FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$39</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
   <si>
     <t>LP</t>
   </si>
@@ -88,66 +88,15 @@
     <t>LP-048472</t>
   </si>
   <si>
-    <t>LP-048580</t>
-  </si>
-  <si>
-    <t>LP-048640</t>
-  </si>
-  <si>
-    <t>LP-048641</t>
-  </si>
-  <si>
-    <t>LP-049056</t>
-  </si>
-  <si>
-    <t>LP-049092</t>
-  </si>
-  <si>
-    <t>LP-049482</t>
-  </si>
-  <si>
     <t>LP-049513</t>
   </si>
   <si>
-    <t>LP-049657</t>
-  </si>
-  <si>
-    <t>LP-049714</t>
-  </si>
-  <si>
     <t>LP-049716</t>
   </si>
   <si>
-    <t>LP-049888</t>
-  </si>
-  <si>
-    <t>LP-050010</t>
-  </si>
-  <si>
-    <t>LP-050262</t>
-  </si>
-  <si>
-    <t>LP-050337</t>
-  </si>
-  <si>
-    <t>LP-050341</t>
-  </si>
-  <si>
     <t>LP-050487</t>
   </si>
   <si>
-    <t>LP-050503</t>
-  </si>
-  <si>
-    <t>LP-050585</t>
-  </si>
-  <si>
-    <t>LP-050609</t>
-  </si>
-  <si>
-    <t>LP-050612</t>
-  </si>
-  <si>
     <t>LP-050693</t>
   </si>
   <si>
@@ -166,9 +115,6 @@
     <t>LP-050888</t>
   </si>
   <si>
-    <t>LP-050992</t>
-  </si>
-  <si>
     <t>LP-051003</t>
   </si>
   <si>
@@ -179,9 +125,6 @@
   </si>
   <si>
     <t>LP-051200</t>
-  </si>
-  <si>
-    <t>LP-051242</t>
   </si>
   <si>
     <t>LP-051290</t>
@@ -559,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -706,205 +649,158 @@
       <c r="A18" t="s">
         <v>19</v>
       </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
+      <c r="B30" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
+      <c r="B31" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E58338-FE9A-4BB8-98AB-E6B221AA88FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9DF041-7A8D-425E-8BCB-66B3D596B653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$39</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
   <si>
     <t>LP</t>
   </si>
@@ -125,15 +122,6 @@
   </si>
   <si>
     <t>LP-051200</t>
-  </si>
-  <si>
-    <t>LP-051290</t>
-  </si>
-  <si>
-    <t>LP-051292</t>
-  </si>
-  <si>
-    <t>LP-051371</t>
   </si>
   <si>
     <t>LP-051464</t>
@@ -502,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -777,30 +765,24 @@
       <c r="A34" t="s">
         <v>34</v>
       </c>
+      <c r="B34" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9DF041-7A8D-425E-8BCB-66B3D596B653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC614E0-49D8-40F4-AD68-35D90D48F075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>LP</t>
   </si>
@@ -28,106 +28,289 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-049934</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-050376</t>
-  </si>
-  <si>
-    <t>LP-050670</t>
-  </si>
-  <si>
-    <t>LP-050714</t>
-  </si>
-  <si>
-    <t>LP-050732</t>
-  </si>
-  <si>
-    <t>LP-050733</t>
-  </si>
-  <si>
-    <t>LP-050734</t>
-  </si>
-  <si>
-    <t>LP-050754</t>
-  </si>
-  <si>
-    <t>LP-050857</t>
-  </si>
-  <si>
-    <t>LP-050894</t>
-  </si>
-  <si>
-    <t>LP-047955</t>
-  </si>
-  <si>
-    <t>LP-047964</t>
-  </si>
-  <si>
-    <t>LP-047987</t>
-  </si>
-  <si>
-    <t>LP-047970</t>
-  </si>
-  <si>
-    <t>LP-048026</t>
-  </si>
-  <si>
-    <t>LP-048427</t>
-  </si>
-  <si>
-    <t>LP-048441</t>
-  </si>
-  <si>
-    <t>LP-048472</t>
-  </si>
-  <si>
-    <t>LP-049513</t>
-  </si>
-  <si>
-    <t>LP-049716</t>
-  </si>
-  <si>
-    <t>LP-050487</t>
-  </si>
-  <si>
-    <t>LP-050693</t>
-  </si>
-  <si>
-    <t>LP-050695</t>
-  </si>
-  <si>
-    <t>LP-050696</t>
-  </si>
-  <si>
-    <t>LP-050743</t>
-  </si>
-  <si>
-    <t>LP-050826</t>
-  </si>
-  <si>
-    <t>LP-050888</t>
-  </si>
-  <si>
-    <t>LP-051003</t>
-  </si>
-  <si>
-    <t>LP-051109</t>
-  </si>
-  <si>
-    <t>LP-051197</t>
-  </si>
-  <si>
-    <t>LP-051200</t>
-  </si>
-  <si>
-    <t>LP-051464</t>
-  </si>
-  <si>
-    <t>LP-051480</t>
+    <t>LP-041815</t>
+  </si>
+  <si>
+    <t>LP-047203</t>
+  </si>
+  <si>
+    <t>LP-047247</t>
+  </si>
+  <si>
+    <t>LP-047835</t>
+  </si>
+  <si>
+    <t>LP-047887</t>
+  </si>
+  <si>
+    <t>LP-047888</t>
+  </si>
+  <si>
+    <t>LP-048163</t>
+  </si>
+  <si>
+    <t>LP-048189</t>
+  </si>
+  <si>
+    <t>LP-048220</t>
+  </si>
+  <si>
+    <t>LP-048659</t>
+  </si>
+  <si>
+    <t>LP-048984</t>
+  </si>
+  <si>
+    <t>LP-048996</t>
+  </si>
+  <si>
+    <t>LP-049690</t>
+  </si>
+  <si>
+    <t>LP-049691</t>
+  </si>
+  <si>
+    <t>LP-049840</t>
+  </si>
+  <si>
+    <t>LP-049841</t>
+  </si>
+  <si>
+    <t>LP-049870</t>
+  </si>
+  <si>
+    <t>LP-049871</t>
+  </si>
+  <si>
+    <t>LP-049954</t>
+  </si>
+  <si>
+    <t>LP-050059</t>
+  </si>
+  <si>
+    <t>LP-050064</t>
+  </si>
+  <si>
+    <t>LP-050088</t>
+  </si>
+  <si>
+    <t>LP-050089</t>
+  </si>
+  <si>
+    <t>LP-050433</t>
+  </si>
+  <si>
+    <t>LP-050436</t>
+  </si>
+  <si>
+    <t>LP-050475</t>
+  </si>
+  <si>
+    <t>LP-050477</t>
+  </si>
+  <si>
+    <t>LP-050528</t>
+  </si>
+  <si>
+    <t>LP-050551</t>
+  </si>
+  <si>
+    <t>LP-050724</t>
+  </si>
+  <si>
+    <t>LP-050981</t>
+  </si>
+  <si>
+    <t>LP-051307</t>
+  </si>
+  <si>
+    <t>LP-033510</t>
+  </si>
+  <si>
+    <t>LP-033548</t>
+  </si>
+  <si>
+    <t>LP-042267</t>
+  </si>
+  <si>
+    <t>LP-047420</t>
+  </si>
+  <si>
+    <t>LP-047986</t>
+  </si>
+  <si>
+    <t>LP-048001</t>
+  </si>
+  <si>
+    <t>LP-048002</t>
+  </si>
+  <si>
+    <t>LP-048178</t>
+  </si>
+  <si>
+    <t>LP-048392</t>
+  </si>
+  <si>
+    <t>LP-048638</t>
+  </si>
+  <si>
+    <t>LP-048663</t>
+  </si>
+  <si>
+    <t>LP-048718</t>
+  </si>
+  <si>
+    <t>LP-049234</t>
+  </si>
+  <si>
+    <t>LP-049371</t>
+  </si>
+  <si>
+    <t>LP-049551</t>
+  </si>
+  <si>
+    <t>LP-049678</t>
+  </si>
+  <si>
+    <t>LP-050030</t>
+  </si>
+  <si>
+    <t>LP-050126</t>
+  </si>
+  <si>
+    <t>LP-050146</t>
+  </si>
+  <si>
+    <t>LP-050150</t>
+  </si>
+  <si>
+    <t>LP-650151</t>
+  </si>
+  <si>
+    <t>LP-050200</t>
+  </si>
+  <si>
+    <t>LP-050272</t>
+  </si>
+  <si>
+    <t>LP-050313</t>
+  </si>
+  <si>
+    <t>LP-050347</t>
+  </si>
+  <si>
+    <t>LP-050359</t>
+  </si>
+  <si>
+    <t>LP-050370</t>
+  </si>
+  <si>
+    <t>LP-050418</t>
+  </si>
+  <si>
+    <t>LP-050424</t>
+  </si>
+  <si>
+    <t>LP-050452</t>
+  </si>
+  <si>
+    <t>LP-050494</t>
+  </si>
+  <si>
+    <t>LP-050498</t>
+  </si>
+  <si>
+    <t>LP-050571</t>
+  </si>
+  <si>
+    <t>LP-050598</t>
+  </si>
+  <si>
+    <t>LP-050599</t>
+  </si>
+  <si>
+    <t>LP-050685</t>
+  </si>
+  <si>
+    <t>LP-050697</t>
+  </si>
+  <si>
+    <t>LP-050325</t>
+  </si>
+  <si>
+    <t>LP-050836</t>
+  </si>
+  <si>
+    <t>LP-050844</t>
+  </si>
+  <si>
+    <t>LP-050926</t>
+  </si>
+  <si>
+    <t>LP-050961</t>
+  </si>
+  <si>
+    <t>LP-050962</t>
+  </si>
+  <si>
+    <t>LP-050982</t>
+  </si>
+  <si>
+    <t>LP-050993</t>
+  </si>
+  <si>
+    <t>LP-050994</t>
+  </si>
+  <si>
+    <t>LP-050995</t>
+  </si>
+  <si>
+    <t>LP-050996</t>
+  </si>
+  <si>
+    <t>LP-050997</t>
+  </si>
+  <si>
+    <t>LP-050998</t>
+  </si>
+  <si>
+    <t>LP-050999</t>
+  </si>
+  <si>
+    <t>LP-051026</t>
+  </si>
+  <si>
+    <t>LP-051105</t>
+  </si>
+  <si>
+    <t>LP-051107</t>
+  </si>
+  <si>
+    <t>LP-051119</t>
+  </si>
+  <si>
+    <t>LP-051128</t>
+  </si>
+  <si>
+    <t>LP-051129</t>
+  </si>
+  <si>
+    <t>LP-051251</t>
+  </si>
+  <si>
+    <t>LP-051259</t>
+  </si>
+  <si>
+    <t>LP-051350</t>
+  </si>
+  <si>
+    <t>LP-051453</t>
+  </si>
+  <si>
+    <t>LP-051500</t>
+  </si>
+  <si>
+    <t>LP-051537</t>
   </si>
 </sst>
 </file>
@@ -490,11 +673,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -509,280 +692,475 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="B32" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="B33" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
-      <c r="B34" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" t="s">
-        <v>3</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCC614E0-49D8-40F4-AD68-35D90D48F075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F98D75-2AD1-4127-88FE-C0B36325D05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$50</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>LP</t>
   </si>
@@ -28,111 +31,33 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-041815</t>
-  </si>
-  <si>
-    <t>LP-047203</t>
-  </si>
-  <si>
-    <t>LP-047247</t>
-  </si>
-  <si>
-    <t>LP-047835</t>
-  </si>
-  <si>
-    <t>LP-047887</t>
-  </si>
-  <si>
-    <t>LP-047888</t>
-  </si>
-  <si>
-    <t>LP-048163</t>
-  </si>
-  <si>
-    <t>LP-048189</t>
-  </si>
-  <si>
-    <t>LP-048220</t>
-  </si>
-  <si>
-    <t>LP-048659</t>
-  </si>
-  <si>
-    <t>LP-048984</t>
-  </si>
-  <si>
-    <t>LP-048996</t>
-  </si>
-  <si>
     <t>LP-049690</t>
   </si>
   <si>
+    <t>Compromisso pendente!</t>
+  </si>
+  <si>
     <t>LP-049691</t>
   </si>
   <si>
-    <t>LP-049840</t>
-  </si>
-  <si>
-    <t>LP-049841</t>
-  </si>
-  <si>
     <t>LP-049870</t>
   </si>
   <si>
     <t>LP-049871</t>
   </si>
   <si>
-    <t>LP-049954</t>
-  </si>
-  <si>
-    <t>LP-050059</t>
-  </si>
-  <si>
-    <t>LP-050064</t>
-  </si>
-  <si>
-    <t>LP-050088</t>
-  </si>
-  <si>
-    <t>LP-050089</t>
-  </si>
-  <si>
-    <t>LP-050433</t>
-  </si>
-  <si>
-    <t>LP-050436</t>
-  </si>
-  <si>
-    <t>LP-050475</t>
-  </si>
-  <si>
-    <t>LP-050477</t>
-  </si>
-  <si>
-    <t>LP-050528</t>
-  </si>
-  <si>
-    <t>LP-050551</t>
-  </si>
-  <si>
     <t>LP-050724</t>
   </si>
   <si>
     <t>LP-050981</t>
   </si>
   <si>
-    <t>LP-051307</t>
-  </si>
-  <si>
     <t>LP-033510</t>
   </si>
   <si>
     <t>LP-033548</t>
   </si>
   <si>
-    <t>LP-042267</t>
-  </si>
-  <si>
     <t>LP-047420</t>
   </si>
   <si>
@@ -151,78 +76,18 @@
     <t>LP-048392</t>
   </si>
   <si>
-    <t>LP-048638</t>
-  </si>
-  <si>
-    <t>LP-048663</t>
-  </si>
-  <si>
-    <t>LP-048718</t>
-  </si>
-  <si>
-    <t>LP-049234</t>
-  </si>
-  <si>
-    <t>LP-049371</t>
-  </si>
-  <si>
-    <t>LP-049551</t>
-  </si>
-  <si>
-    <t>LP-049678</t>
-  </si>
-  <si>
-    <t>LP-050030</t>
-  </si>
-  <si>
-    <t>LP-050126</t>
-  </si>
-  <si>
-    <t>LP-050146</t>
-  </si>
-  <si>
     <t>LP-050150</t>
   </si>
   <si>
-    <t>LP-650151</t>
-  </si>
-  <si>
-    <t>LP-050200</t>
-  </si>
-  <si>
-    <t>LP-050272</t>
-  </si>
-  <si>
-    <t>LP-050313</t>
-  </si>
-  <si>
-    <t>LP-050347</t>
-  </si>
-  <si>
     <t>LP-050359</t>
   </si>
   <si>
-    <t>LP-050370</t>
-  </si>
-  <si>
-    <t>LP-050418</t>
-  </si>
-  <si>
-    <t>LP-050424</t>
-  </si>
-  <si>
-    <t>LP-050452</t>
-  </si>
-  <si>
     <t>LP-050494</t>
   </si>
   <si>
     <t>LP-050498</t>
   </si>
   <si>
-    <t>LP-050571</t>
-  </si>
-  <si>
     <t>LP-050598</t>
   </si>
   <si>
@@ -311,6 +176,9 @@
   </si>
   <si>
     <t>LP-051537</t>
+  </si>
+  <si>
+    <t>LP-050151</t>
   </si>
 </sst>
 </file>
@@ -673,11 +541,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -692,153 +560,207 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -931,236 +853,6 @@
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F98D75-2AD1-4127-88FE-C0B36325D05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A31D3C-1616-44CA-A654-BAB3A1B75121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$50</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
   <si>
     <t>LP</t>
   </si>
@@ -88,6 +85,9 @@
     <t>LP-050498</t>
   </si>
   <si>
+    <t>LP-050151</t>
+  </si>
+  <si>
     <t>LP-050598</t>
   </si>
   <si>
@@ -163,9 +163,6 @@
     <t>LP-051251</t>
   </si>
   <si>
-    <t>LP-051259</t>
-  </si>
-  <si>
     <t>LP-051350</t>
   </si>
   <si>
@@ -176,9 +173,6 @@
   </si>
   <si>
     <t>LP-051537</t>
-  </si>
-  <si>
-    <t>LP-050151</t>
   </si>
 </sst>
 </file>
@@ -541,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -702,157 +696,188 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>39</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>40</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>42</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>45</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>46</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>47</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>48</v>
+      </c>
+      <c r="B29" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>49</v>
+      </c>
+      <c r="B30" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="B31" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Open-LPs.xlsx
+++ b/Open-LPs.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A31D3C-1616-44CA-A654-BAB3A1B75121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFC5B28-5A94-4314-94DF-E3CBD935B6D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="388">
   <si>
     <t>LP</t>
   </si>
@@ -28,63 +41,6 @@
     <t>Status</t>
   </si>
   <si>
-    <t>LP-049690</t>
-  </si>
-  <si>
-    <t>Compromisso pendente!</t>
-  </si>
-  <si>
-    <t>LP-049691</t>
-  </si>
-  <si>
-    <t>LP-049870</t>
-  </si>
-  <si>
-    <t>LP-049871</t>
-  </si>
-  <si>
-    <t>LP-050724</t>
-  </si>
-  <si>
-    <t>LP-050981</t>
-  </si>
-  <si>
-    <t>LP-033510</t>
-  </si>
-  <si>
-    <t>LP-033548</t>
-  </si>
-  <si>
-    <t>LP-047420</t>
-  </si>
-  <si>
-    <t>LP-047986</t>
-  </si>
-  <si>
-    <t>LP-048001</t>
-  </si>
-  <si>
-    <t>LP-048002</t>
-  </si>
-  <si>
-    <t>LP-048178</t>
-  </si>
-  <si>
-    <t>LP-048392</t>
-  </si>
-  <si>
-    <t>LP-050150</t>
-  </si>
-  <si>
-    <t>LP-050359</t>
-  </si>
-  <si>
-    <t>LP-050494</t>
-  </si>
-  <si>
-    <t>LP-050498</t>
-  </si>
-  <si>
     <t>LP-050151</t>
   </si>
   <si>
@@ -139,40 +95,1108 @@
     <t>LP-050998</t>
   </si>
   <si>
-    <t>LP-050999</t>
-  </si>
-  <si>
-    <t>LP-051026</t>
-  </si>
-  <si>
-    <t>LP-051105</t>
-  </si>
-  <si>
-    <t>LP-051107</t>
-  </si>
-  <si>
-    <t>LP-051119</t>
-  </si>
-  <si>
-    <t>LP-051128</t>
-  </si>
-  <si>
-    <t>LP-051129</t>
-  </si>
-  <si>
-    <t>LP-051251</t>
-  </si>
-  <si>
-    <t>LP-051350</t>
-  </si>
-  <si>
-    <t>LP-051453</t>
-  </si>
-  <si>
-    <t>LP-051500</t>
-  </si>
-  <si>
-    <t>LP-051537</t>
+    <t>LP-046252</t>
+  </si>
+  <si>
+    <t>LP-050112</t>
+  </si>
+  <si>
+    <t>LP-050247</t>
+  </si>
+  <si>
+    <t>LP-050356</t>
+  </si>
+  <si>
+    <t>LP-050357</t>
+  </si>
+  <si>
+    <t>LP-050363</t>
+  </si>
+  <si>
+    <t>LP-050440</t>
+  </si>
+  <si>
+    <t>LP-050454</t>
+  </si>
+  <si>
+    <t>LP-050554</t>
+  </si>
+  <si>
+    <t>LP-050574</t>
+  </si>
+  <si>
+    <t>LP-050593</t>
+  </si>
+  <si>
+    <t>LP-050607</t>
+  </si>
+  <si>
+    <t>LP-050620</t>
+  </si>
+  <si>
+    <t>LP-050621</t>
+  </si>
+  <si>
+    <t>LP-050630</t>
+  </si>
+  <si>
+    <t>LP-050699</t>
+  </si>
+  <si>
+    <t>LP-050708</t>
+  </si>
+  <si>
+    <t>LP-050774</t>
+  </si>
+  <si>
+    <t>LP-050840</t>
+  </si>
+  <si>
+    <t>LP-050862</t>
+  </si>
+  <si>
+    <t>LP-050878</t>
+  </si>
+  <si>
+    <t>LP-050896</t>
+  </si>
+  <si>
+    <t>LP-050899</t>
+  </si>
+  <si>
+    <t>LP-050923</t>
+  </si>
+  <si>
+    <t>LP-050924</t>
+  </si>
+  <si>
+    <t>LP-050925</t>
+  </si>
+  <si>
+    <t>LP-051932</t>
+  </si>
+  <si>
+    <t>LP-050939</t>
+  </si>
+  <si>
+    <t>LP-050959</t>
+  </si>
+  <si>
+    <t>LP-050960</t>
+  </si>
+  <si>
+    <t>LP-050983</t>
+  </si>
+  <si>
+    <t>LP-051006</t>
+  </si>
+  <si>
+    <t>LP-051012</t>
+  </si>
+  <si>
+    <t>LP-051061</t>
+  </si>
+  <si>
+    <t>LP-051052</t>
+  </si>
+  <si>
+    <t>LP-051093</t>
+  </si>
+  <si>
+    <t>LP-051100</t>
+  </si>
+  <si>
+    <t>LP-051101</t>
+  </si>
+  <si>
+    <t>LP-051116</t>
+  </si>
+  <si>
+    <t>LP-051136</t>
+  </si>
+  <si>
+    <t>LP-051179</t>
+  </si>
+  <si>
+    <t>LP-051272</t>
+  </si>
+  <si>
+    <t>LP-051273</t>
+  </si>
+  <si>
+    <t>LP-051274</t>
+  </si>
+  <si>
+    <t>LP-051280</t>
+  </si>
+  <si>
+    <t>LP-051404</t>
+  </si>
+  <si>
+    <t>LP-051408</t>
+  </si>
+  <si>
+    <t>LP-051503</t>
+  </si>
+  <si>
+    <t>LP-051576</t>
+  </si>
+  <si>
+    <t>LP-051594</t>
+  </si>
+  <si>
+    <t>LP-051602</t>
+  </si>
+  <si>
+    <t>LP-051660</t>
+  </si>
+  <si>
+    <t>LP-051708</t>
+  </si>
+  <si>
+    <t>LP-051769</t>
+  </si>
+  <si>
+    <t>LP-051983</t>
+  </si>
+  <si>
+    <t>LP-052036</t>
+  </si>
+  <si>
+    <t>LP-052052</t>
+  </si>
+  <si>
+    <t>LP-052157</t>
+  </si>
+  <si>
+    <t>LP-052201</t>
+  </si>
+  <si>
+    <t>LP-052210</t>
+  </si>
+  <si>
+    <t>LP-046404</t>
+  </si>
+  <si>
+    <t>LP-047019</t>
+  </si>
+  <si>
+    <t>LP-047740</t>
+  </si>
+  <si>
+    <t>LP-049256</t>
+  </si>
+  <si>
+    <t>LP-049915</t>
+  </si>
+  <si>
+    <t>LP-050366</t>
+  </si>
+  <si>
+    <t>LP-050367</t>
+  </si>
+  <si>
+    <t>LP-050486</t>
+  </si>
+  <si>
+    <t>LP-050565</t>
+  </si>
+  <si>
+    <t>LP-050631</t>
+  </si>
+  <si>
+    <t>LP-050632</t>
+  </si>
+  <si>
+    <t>LP-050633</t>
+  </si>
+  <si>
+    <t>LP-050635</t>
+  </si>
+  <si>
+    <t>LP-050827</t>
+  </si>
+  <si>
+    <t>LP-050839</t>
+  </si>
+  <si>
+    <t>LP-050858</t>
+  </si>
+  <si>
+    <t>LP-050859</t>
+  </si>
+  <si>
+    <t>LP-050873</t>
+  </si>
+  <si>
+    <t>LP-050929</t>
+  </si>
+  <si>
+    <t>LP-050956</t>
+  </si>
+  <si>
+    <t>LP-050958</t>
+  </si>
+  <si>
+    <t>LP-050986</t>
+  </si>
+  <si>
+    <t>LP-051060</t>
+  </si>
+  <si>
+    <t>LP-051094</t>
+  </si>
+  <si>
+    <t>LP-051112</t>
+  </si>
+  <si>
+    <t>LP-051163</t>
+  </si>
+  <si>
+    <t>LP-051230</t>
+  </si>
+  <si>
+    <t>LP-051231</t>
+  </si>
+  <si>
+    <t>LP-051270</t>
+  </si>
+  <si>
+    <t>LP-051357</t>
+  </si>
+  <si>
+    <t>LP-051400</t>
+  </si>
+  <si>
+    <t>LP-051406</t>
+  </si>
+  <si>
+    <t>LP-051455</t>
+  </si>
+  <si>
+    <t>LP-051456</t>
+  </si>
+  <si>
+    <t>LP-051484</t>
+  </si>
+  <si>
+    <t>LP-051570</t>
+  </si>
+  <si>
+    <t>LP-051592</t>
+  </si>
+  <si>
+    <t>LP-051629</t>
+  </si>
+  <si>
+    <t>LP-051662</t>
+  </si>
+  <si>
+    <t>LP-051666</t>
+  </si>
+  <si>
+    <t>LP-051667</t>
+  </si>
+  <si>
+    <t>LP-051684</t>
+  </si>
+  <si>
+    <t>LP-051747</t>
+  </si>
+  <si>
+    <t>LP-051844</t>
+  </si>
+  <si>
+    <t>LP-051845</t>
+  </si>
+  <si>
+    <t>LP-051846</t>
+  </si>
+  <si>
+    <t>LP-051847</t>
+  </si>
+  <si>
+    <t>LP-051855</t>
+  </si>
+  <si>
+    <t>LP-051857</t>
+  </si>
+  <si>
+    <t>LP-051859</t>
+  </si>
+  <si>
+    <t>LP-051861</t>
+  </si>
+  <si>
+    <t>LP-051865</t>
+  </si>
+  <si>
+    <t>LP-051866</t>
+  </si>
+  <si>
+    <t>LP-051871</t>
+  </si>
+  <si>
+    <t>LP-051901</t>
+  </si>
+  <si>
+    <t>LP-051919</t>
+  </si>
+  <si>
+    <t>LP-051931</t>
+  </si>
+  <si>
+    <t>LP-052006</t>
+  </si>
+  <si>
+    <t>LP-052007</t>
+  </si>
+  <si>
+    <t>LP-052019</t>
+  </si>
+  <si>
+    <t>LP-052021</t>
+  </si>
+  <si>
+    <t>LP-052083</t>
+  </si>
+  <si>
+    <t>LP-052086</t>
+  </si>
+  <si>
+    <t>LP-052094</t>
+  </si>
+  <si>
+    <t>LP-052095</t>
+  </si>
+  <si>
+    <t>LP-052166</t>
+  </si>
+  <si>
+    <t>LP-052197</t>
+  </si>
+  <si>
+    <t>LP-052211</t>
+  </si>
+  <si>
+    <t>LP-052295</t>
+  </si>
+  <si>
+    <t>LP-052299</t>
+  </si>
+  <si>
+    <t>LP-033611</t>
+  </si>
+  <si>
+    <t>LP-040735</t>
+  </si>
+  <si>
+    <t>LP-043162</t>
+  </si>
+  <si>
+    <t>LP-043280</t>
+  </si>
+  <si>
+    <t>LP-043975</t>
+  </si>
+  <si>
+    <t>LP-044234</t>
+  </si>
+  <si>
+    <t>LP-045835</t>
+  </si>
+  <si>
+    <t>LP-045874</t>
+  </si>
+  <si>
+    <t>LP-045877</t>
+  </si>
+  <si>
+    <t>LP-046519</t>
+  </si>
+  <si>
+    <t>LP-046966</t>
+  </si>
+  <si>
+    <t>LP-047977</t>
+  </si>
+  <si>
+    <t>LP-047988</t>
+  </si>
+  <si>
+    <t>LP-048161</t>
+  </si>
+  <si>
+    <t>LP-048171</t>
+  </si>
+  <si>
+    <t>LP-048177</t>
+  </si>
+  <si>
+    <t>LP-048357</t>
+  </si>
+  <si>
+    <t>LP-048362</t>
+  </si>
+  <si>
+    <t>LP-049234</t>
+  </si>
+  <si>
+    <t>LP-049329</t>
+  </si>
+  <si>
+    <t>LP-049973</t>
+  </si>
+  <si>
+    <t>LP-050406</t>
+  </si>
+  <si>
+    <t>LP-050453</t>
+  </si>
+  <si>
+    <t>LP-050457</t>
+  </si>
+  <si>
+    <t>LP-050517</t>
+  </si>
+  <si>
+    <t>LP-050538</t>
+  </si>
+  <si>
+    <t>LP-050608</t>
+  </si>
+  <si>
+    <t>LP-050765</t>
+  </si>
+  <si>
+    <t>LP-050766</t>
+  </si>
+  <si>
+    <t>LP-050782</t>
+  </si>
+  <si>
+    <t>LP-050837</t>
+  </si>
+  <si>
+    <t>LP-050860</t>
+  </si>
+  <si>
+    <t>LP-050868</t>
+  </si>
+  <si>
+    <t>LP-050869</t>
+  </si>
+  <si>
+    <t>LP-050918</t>
+  </si>
+  <si>
+    <t>LP-050973</t>
+  </si>
+  <si>
+    <t>LP-050977</t>
+  </si>
+  <si>
+    <t>LP-050987</t>
+  </si>
+  <si>
+    <t>LP-050988</t>
+  </si>
+  <si>
+    <t>LP-051014</t>
+  </si>
+  <si>
+    <t>LP-051015</t>
+  </si>
+  <si>
+    <t>LP-051090</t>
+  </si>
+  <si>
+    <t>LP-051092</t>
+  </si>
+  <si>
+    <t>LP-051108</t>
+  </si>
+  <si>
+    <t>LP-051113</t>
+  </si>
+  <si>
+    <t>LP-051126</t>
+  </si>
+  <si>
+    <t>LP-051165</t>
+  </si>
+  <si>
+    <t>LP-051212</t>
+  </si>
+  <si>
+    <t>LP-051227</t>
+  </si>
+  <si>
+    <t>LP-051234</t>
+  </si>
+  <si>
+    <t>LP-051236</t>
+  </si>
+  <si>
+    <t>LP-051358</t>
+  </si>
+  <si>
+    <t>LP-051375</t>
+  </si>
+  <si>
+    <t>LP-051409</t>
+  </si>
+  <si>
+    <t>LP-051498</t>
+  </si>
+  <si>
+    <t>LP-051501</t>
+  </si>
+  <si>
+    <t>LP-051502</t>
+  </si>
+  <si>
+    <t>LP-051506</t>
+  </si>
+  <si>
+    <t>LP-051507</t>
+  </si>
+  <si>
+    <t>LP-051524</t>
+  </si>
+  <si>
+    <t>LP-051601</t>
+  </si>
+  <si>
+    <t>LP-051603</t>
+  </si>
+  <si>
+    <t>LP-051604</t>
+  </si>
+  <si>
+    <t>LP-051605</t>
+  </si>
+  <si>
+    <t>LP-051646</t>
+  </si>
+  <si>
+    <t>LP-051647</t>
+  </si>
+  <si>
+    <t>LP-051648</t>
+  </si>
+  <si>
+    <t>LP-051649</t>
+  </si>
+  <si>
+    <t>LP-051650</t>
+  </si>
+  <si>
+    <t>LP-051651</t>
+  </si>
+  <si>
+    <t>LP-051652</t>
+  </si>
+  <si>
+    <t>LP-051653</t>
+  </si>
+  <si>
+    <t>LP-051654</t>
+  </si>
+  <si>
+    <t>LP-051655</t>
+  </si>
+  <si>
+    <t>LP-051664</t>
+  </si>
+  <si>
+    <t>LP-051665</t>
+  </si>
+  <si>
+    <t>LP-051886</t>
+  </si>
+  <si>
+    <t>LP-051893</t>
+  </si>
+  <si>
+    <t>LP-051918</t>
+  </si>
+  <si>
+    <t>LP-052037</t>
+  </si>
+  <si>
+    <t>LP-052348</t>
+  </si>
+  <si>
+    <t>LP-052349</t>
+  </si>
+  <si>
+    <t>LP-052354</t>
+  </si>
+  <si>
+    <t>LP-052392</t>
+  </si>
+  <si>
+    <t>LP-052444</t>
+  </si>
+  <si>
+    <t>LP-052466</t>
+  </si>
+  <si>
+    <t>LP-040674</t>
+  </si>
+  <si>
+    <t>LP-046158</t>
+  </si>
+  <si>
+    <t>LP-047205</t>
+  </si>
+  <si>
+    <t>LP-049046</t>
+  </si>
+  <si>
+    <t>LP-049350</t>
+  </si>
+  <si>
+    <t>LP-049758</t>
+  </si>
+  <si>
+    <t>LP-049963</t>
+  </si>
+  <si>
+    <t>LP-050031</t>
+  </si>
+  <si>
+    <t>LP-050095</t>
+  </si>
+  <si>
+    <t>LP-050407</t>
+  </si>
+  <si>
+    <t>LP-050415</t>
+  </si>
+  <si>
+    <t>LP-050667</t>
+  </si>
+  <si>
+    <t>LP-050729</t>
+  </si>
+  <si>
+    <t>LP-051036</t>
+  </si>
+  <si>
+    <t>LP-051067</t>
+  </si>
+  <si>
+    <t>LP-051077</t>
+  </si>
+  <si>
+    <t>LP-051080</t>
+  </si>
+  <si>
+    <t>LP-051082</t>
+  </si>
+  <si>
+    <t>LP-051083</t>
+  </si>
+  <si>
+    <t>LP-051159</t>
+  </si>
+  <si>
+    <t>LP-051160</t>
+  </si>
+  <si>
+    <t>LP-051379</t>
+  </si>
+  <si>
+    <t>LP-051385</t>
+  </si>
+  <si>
+    <t>LP-051386</t>
+  </si>
+  <si>
+    <t>LP-051422</t>
+  </si>
+  <si>
+    <t>LP-051428</t>
+  </si>
+  <si>
+    <t>LP-051485</t>
+  </si>
+  <si>
+    <t>LP-052188</t>
+  </si>
+  <si>
+    <t>LP-044816</t>
+  </si>
+  <si>
+    <t>LP-045910</t>
+  </si>
+  <si>
+    <t>LP-046171</t>
+  </si>
+  <si>
+    <t>LP-046811</t>
+  </si>
+  <si>
+    <t>LP-047333</t>
+  </si>
+  <si>
+    <t>LP-047840</t>
+  </si>
+  <si>
+    <t>LP-048259</t>
+  </si>
+  <si>
+    <t>LP-048389</t>
+  </si>
+  <si>
+    <t>LP-048982</t>
+  </si>
+  <si>
+    <t>LP-049000</t>
+  </si>
+  <si>
+    <t>LP-049035</t>
+  </si>
+  <si>
+    <t>LP-049119</t>
+  </si>
+  <si>
+    <t>LP-049142</t>
+  </si>
+  <si>
+    <t>LP-049162</t>
+  </si>
+  <si>
+    <t>LP-049333</t>
+  </si>
+  <si>
+    <t>LP-049343</t>
+  </si>
+  <si>
+    <t>LP-049347</t>
+  </si>
+  <si>
+    <t>LP-049359</t>
+  </si>
+  <si>
+    <t>LP-049375</t>
+  </si>
+  <si>
+    <t>LP-049383</t>
+  </si>
+  <si>
+    <t>LP-049465</t>
+  </si>
+  <si>
+    <t>LP-049507</t>
+  </si>
+  <si>
+    <t>LP-049663</t>
+  </si>
+  <si>
+    <t>LP-049664</t>
+  </si>
+  <si>
+    <t>LP-049667</t>
+  </si>
+  <si>
+    <t>LP-049771</t>
+  </si>
+  <si>
+    <t>LP-049772</t>
+  </si>
+  <si>
+    <t>LP-049850</t>
+  </si>
+  <si>
+    <t>LP-549852</t>
+  </si>
+  <si>
+    <t>LP-049969</t>
+  </si>
+  <si>
+    <t>LP-049970</t>
+  </si>
+  <si>
+    <t>LP-050125</t>
+  </si>
+  <si>
+    <t>LP-050155</t>
+  </si>
+  <si>
+    <t>LP-050256</t>
+  </si>
+  <si>
+    <t>LP-050276</t>
+  </si>
+  <si>
+    <t>LP-050393</t>
+  </si>
+  <si>
+    <t>LP-050402</t>
+  </si>
+  <si>
+    <t>LP-050414</t>
+  </si>
+  <si>
+    <t>LP-050434</t>
+  </si>
+  <si>
+    <t>LP-050437</t>
+  </si>
+  <si>
+    <t>LP-050471</t>
+  </si>
+  <si>
+    <t>LP-050719</t>
+  </si>
+  <si>
+    <t>LP-050721</t>
+  </si>
+  <si>
+    <t>LP-050749</t>
+  </si>
+  <si>
+    <t>LP-050751</t>
+  </si>
+  <si>
+    <t>LP-050867</t>
+  </si>
+  <si>
+    <t>LP-051076</t>
+  </si>
+  <si>
+    <t>LP-051078</t>
+  </si>
+  <si>
+    <t>LP-051081</t>
+  </si>
+  <si>
+    <t>LP-051084</t>
+  </si>
+  <si>
+    <t>LP-051087</t>
+  </si>
+  <si>
+    <t>LP-051138</t>
+  </si>
+  <si>
+    <t>LP-051157</t>
+  </si>
+  <si>
+    <t>LP-051158</t>
+  </si>
+  <si>
+    <t>LP-051256</t>
+  </si>
+  <si>
+    <t>LP-051282</t>
+  </si>
+  <si>
+    <t>LP-051283</t>
+  </si>
+  <si>
+    <t>LP-051300</t>
+  </si>
+  <si>
+    <t>LP-051301</t>
+  </si>
+  <si>
+    <t>LP-051423</t>
+  </si>
+  <si>
+    <t>LP-051492</t>
+  </si>
+  <si>
+    <t>LP-051520</t>
+  </si>
+  <si>
+    <t>LP-051522</t>
+  </si>
+  <si>
+    <t>LP-051539</t>
+  </si>
+  <si>
+    <t>LP-051545</t>
+  </si>
+  <si>
+    <t>LP-051718</t>
+  </si>
+  <si>
+    <t>LP-051719</t>
+  </si>
+  <si>
+    <t>LP-051728</t>
+  </si>
+  <si>
+    <t>LP-051729</t>
+  </si>
+  <si>
+    <t>LP-052098</t>
+  </si>
+  <si>
+    <t>LP-044462</t>
+  </si>
+  <si>
+    <t>LP-045222</t>
+  </si>
+  <si>
+    <t>LP-047092</t>
+  </si>
+  <si>
+    <t>LP-047257</t>
+  </si>
+  <si>
+    <t>LP-047258</t>
+  </si>
+  <si>
+    <t>LP-047283</t>
+  </si>
+  <si>
+    <t>LP-047287</t>
+  </si>
+  <si>
+    <t>LP-047294</t>
+  </si>
+  <si>
+    <t>LP-047454</t>
+  </si>
+  <si>
+    <t>LP-047549</t>
+  </si>
+  <si>
+    <t>LP-047778</t>
+  </si>
+  <si>
+    <t>LP-047989</t>
+  </si>
+  <si>
+    <t>LP-047991</t>
+  </si>
+  <si>
+    <t>LP-048010</t>
+  </si>
+  <si>
+    <t>LP-048343</t>
+  </si>
+  <si>
+    <t>LP-048351</t>
+  </si>
+  <si>
+    <t>LP-048397</t>
+  </si>
+  <si>
+    <t>LP-048426</t>
+  </si>
+  <si>
+    <t>LP-049431</t>
+  </si>
+  <si>
+    <t>LP-050098</t>
+  </si>
+  <si>
+    <t>LP-050137</t>
+  </si>
+  <si>
+    <t>LP-050248</t>
+  </si>
+  <si>
+    <t>LP-050310</t>
+  </si>
+  <si>
+    <t>LP-050445</t>
+  </si>
+  <si>
+    <t>LP-050895</t>
+  </si>
+  <si>
+    <t>LP-051011</t>
+  </si>
+  <si>
+    <t>LP-051095</t>
+  </si>
+  <si>
+    <t>LP-051172</t>
+  </si>
+  <si>
+    <t>LP-051224</t>
+  </si>
+  <si>
+    <t>LP-051318</t>
+  </si>
+  <si>
+    <t>LP-051319</t>
+  </si>
+  <si>
+    <t>LP-051383</t>
+  </si>
+  <si>
+    <t>LP-051436</t>
+  </si>
+  <si>
+    <t>LP-051626</t>
+  </si>
+  <si>
+    <t>LP-051658</t>
+  </si>
+  <si>
+    <t>LP-051663</t>
+  </si>
+  <si>
+    <t>LP-051756</t>
+  </si>
+  <si>
+    <t>LP-051775</t>
+  </si>
+  <si>
+    <t>LP-051938</t>
+  </si>
+  <si>
+    <t>LP-051967</t>
+  </si>
+  <si>
+    <t>LP-052088</t>
+  </si>
+  <si>
+    <t>LP-052110</t>
+  </si>
+  <si>
+    <t>LP-052133</t>
+  </si>
+  <si>
+    <t>LP-052155</t>
+  </si>
+  <si>
+    <t>LP-052192</t>
+  </si>
+  <si>
+    <t>LP-052253</t>
+  </si>
+  <si>
+    <t>LP-052430</t>
+  </si>
+  <si>
+    <t>LP-052465</t>
+  </si>
+  <si>
+    <t>LP-052479</t>
+  </si>
+  <si>
+    <t>LP-052511</t>
+  </si>
+  <si>
+    <t>LP-052512</t>
+  </si>
+  <si>
+    <t>LP-052516</t>
+  </si>
+  <si>
+    <t>LP-052518</t>
+  </si>
+  <si>
+    <t>LP-052537</t>
   </si>
 </sst>
 </file>
@@ -535,11 +1559,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B389"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -554,330 +1578,1940 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>38</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
